--- a/inputdata/inputdata_hybridAC.xlsx
+++ b/inputdata/inputdata_hybridAC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Itahisa\Desktop\pvlite\inputdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E749C60-27D6-4753-B650-0F6FF9E429EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898FF1D6-F9B6-4D93-A498-D1ABC6E8A16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="2475" windowWidth="21840" windowHeight="13290" tabRatio="833" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site" sheetId="6" r:id="rId1"/>
@@ -1192,9 +1192,6 @@
     <t>Use_Database_PV</t>
   </si>
   <si>
-    <t>N_modules</t>
-  </si>
-  <si>
     <t>Use_Database_Inv</t>
   </si>
   <si>
@@ -1253,6 +1250,9 @@
   </si>
   <si>
     <t>Set to 2 to use PVlite database (1 = Manual Mode, 2 = Use Database)</t>
+  </si>
+  <si>
+    <t>N_Modules</t>
   </si>
 </sst>
 </file>
@@ -1264,7 +1264,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -7652,7 +7652,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="20.109375" style="2" customWidth="1"/>
@@ -7663,7 +7663,7 @@
     <col min="7" max="16384" width="11.44140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.4">
+    <row r="1" spans="1:6" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>16</v>
       </c>
@@ -7671,7 +7671,7 @@
       <c r="D1" s="79"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
         <v>8</v>
@@ -7686,7 +7686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -7720,7 +7720,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -7754,17 +7754,17 @@
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="E9"/>
       <c r="F9" s="10"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="F13"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="E14"/>
     </row>
   </sheetData>
@@ -7803,7 +7803,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:I26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.44140625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
@@ -7813,7 +7813,7 @@
     <col min="6" max="6" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.4">
+    <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="11"/>
       <c r="B1" s="79" t="s">
         <v>107</v>
@@ -7822,14 +7822,14 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:9" ht="17.399999999999999">
+    <row r="2" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="11"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="17.399999999999999">
+    <row r="3" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A3" s="11"/>
       <c r="B3" s="4" t="s">
         <v>8</v>
@@ -7844,7 +7844,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="19.5" customHeight="1">
+    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="F4" s="63"/>
     </row>
-    <row r="5" spans="1:9" ht="17.399999999999999">
+    <row r="5" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -7879,7 +7879,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="20.25" customHeight="1">
+    <row r="6" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -7896,13 +7896,13 @@
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15">
+    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A7" s="24">
         <v>4</v>
       </c>
       <c r="D7" s="11"/>
     </row>
-    <row r="8" spans="1:9" ht="17.399999999999999">
+    <row r="8" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -7919,7 +7919,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="19.5" customHeight="1">
+    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -7936,7 +7936,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="21" customHeight="1">
+    <row r="10" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -7954,7 +7954,7 @@
       </c>
       <c r="I10" s="27"/>
     </row>
-    <row r="11" spans="1:9" ht="19.5" customHeight="1">
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -7971,7 +7971,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="19.5" customHeight="1">
+    <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="19.5" customHeight="1">
+    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -7997,7 +7997,7 @@
       <c r="D13" s="87"/>
       <c r="E13" s="27"/>
     </row>
-    <row r="14" spans="1:9" ht="19.5" customHeight="1">
+    <row r="14" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="24">
         <v>11</v>
       </c>
@@ -8008,7 +8008,7 @@
       <c r="D14" s="87"/>
       <c r="E14" s="27"/>
     </row>
-    <row r="15" spans="1:9" ht="19.5" customHeight="1">
+    <row r="15" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="24">
         <v>12</v>
       </c>
@@ -8021,7 +8021,7 @@
       <c r="D15" s="87"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="1:9" ht="19.5" customHeight="1">
+    <row r="16" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="24">
         <v>13</v>
       </c>
@@ -8035,7 +8035,7 @@
       <c r="D16" s="87"/>
       <c r="E16" s="27"/>
     </row>
-    <row r="17" spans="1:5" ht="17.399999999999999">
+    <row r="17" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A17" s="24">
         <v>14</v>
       </c>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="D17" s="11"/>
     </row>
-    <row r="18" spans="1:5" ht="17.399999999999999">
+    <row r="18" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A18" s="24">
         <v>15</v>
       </c>
@@ -8064,7 +8064,7 @@
       <c r="D18" s="12"/>
       <c r="E18" s="25"/>
     </row>
-    <row r="19" spans="1:5" ht="17.399999999999999">
+    <row r="19" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A19" s="24">
         <v>16</v>
       </c>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="D19" s="33"/>
     </row>
-    <row r="20" spans="1:5" ht="17.399999999999999">
+    <row r="20" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A20" s="24">
         <v>17</v>
       </c>
@@ -8093,25 +8093,25 @@
       <c r="D20" s="33"/>
       <c r="E20" s="27"/>
     </row>
-    <row r="21" spans="1:5" ht="17.399999999999999">
+    <row r="21" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="D21" s="33"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5" ht="17.399999999999999">
+    <row r="22" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="D22" s="9"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5" ht="17.399999999999999">
+    <row r="23" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="D23" s="9"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5" ht="17.399999999999999">
+    <row r="24" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="D24" s="9"/>
     </row>
-    <row r="25" spans="1:5" ht="15">
+    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="D25" s="11"/>
     </row>
-    <row r="26" spans="1:5" ht="15">
+    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="D26" s="11"/>
     </row>
   </sheetData>
@@ -8129,7 +8129,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:L20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5546875" customWidth="1"/>
     <col min="2" max="2" width="19.5546875" customWidth="1"/>
@@ -8138,7 +8138,7 @@
     <col min="5" max="5" width="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="23.4">
+    <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="11"/>
       <c r="B1" s="79" t="s">
         <v>153</v>
@@ -8147,14 +8147,14 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:12" ht="17.399999999999999">
+    <row r="2" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="11"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="17.399999999999999">
+    <row r="3" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A3" s="11"/>
       <c r="B3" s="4" t="s">
         <v>8</v>
@@ -8172,7 +8172,7 @@
       <c r="K3" s="92"/>
       <c r="L3" s="92"/>
     </row>
-    <row r="4" spans="1:12" ht="19.5" customHeight="1">
+    <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -8193,7 +8193,7 @@
       <c r="K4" s="92"/>
       <c r="L4" s="92"/>
     </row>
-    <row r="5" spans="1:12" ht="22.5" customHeight="1">
+    <row r="5" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -8213,7 +8213,7 @@
       <c r="K5" s="92"/>
       <c r="L5" s="92"/>
     </row>
-    <row r="6" spans="1:12" ht="21" customHeight="1">
+    <row r="6" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -8233,7 +8233,7 @@
       <c r="K6" s="92"/>
       <c r="L6" s="92"/>
     </row>
-    <row r="7" spans="1:12" ht="17.399999999999999">
+    <row r="7" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -8250,7 +8250,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="19.5" customHeight="1">
+    <row r="8" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="F8" s="25"/>
     </row>
-    <row r="9" spans="1:12" ht="17.399999999999999">
+    <row r="9" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -8282,7 +8282,7 @@
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
     </row>
-    <row r="10" spans="1:12" ht="19.5" customHeight="1">
+    <row r="10" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -8295,7 +8295,7 @@
       <c r="D10" s="87"/>
       <c r="E10" s="27"/>
     </row>
-    <row r="11" spans="1:12" ht="19.5" customHeight="1">
+    <row r="11" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -8308,7 +8308,7 @@
       <c r="D11" s="87"/>
       <c r="E11" s="27"/>
     </row>
-    <row r="12" spans="1:12" ht="17.399999999999999">
+    <row r="12" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:12" ht="17.399999999999999">
+    <row r="13" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -8336,7 +8336,7 @@
       <c r="D13" s="12"/>
       <c r="E13" s="25"/>
     </row>
-    <row r="14" spans="1:12" ht="17.399999999999999">
+    <row r="14" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="24">
         <v>11</v>
       </c>
@@ -8350,7 +8350,7 @@
       </c>
       <c r="D14" s="33"/>
     </row>
-    <row r="15" spans="1:12" ht="17.399999999999999">
+    <row r="15" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="24">
         <v>12</v>
       </c>
@@ -8365,7 +8365,7 @@
       <c r="D15" s="33"/>
       <c r="E15" s="27"/>
     </row>
-    <row r="16" spans="1:12" ht="17.399999999999999">
+    <row r="16" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A16" s="24">
         <v>13</v>
       </c>
@@ -8380,7 +8380,7 @@
       <c r="D16" s="33"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" ht="17.399999999999999">
+    <row r="17" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A17" s="24">
         <v>14</v>
       </c>
@@ -8395,7 +8395,7 @@
       <c r="D17" s="9"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" ht="17.399999999999999">
+    <row r="18" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A18" s="24">
         <v>15</v>
       </c>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="D18" s="9"/>
     </row>
-    <row r="19" spans="1:5" ht="17.399999999999999">
+    <row r="19" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A19" s="24">
         <v>16</v>
       </c>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="D19" s="11"/>
     </row>
-    <row r="20" spans="1:5" ht="15">
+    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="D20" s="11"/>
     </row>
   </sheetData>
@@ -8441,7 +8441,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:F95"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.44140625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -8451,7 +8451,7 @@
     <col min="6" max="6" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="11"/>
       <c r="B1" s="79" t="s">
         <v>51</v>
@@ -8460,14 +8460,14 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999">
+    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="11"/>
       <c r="B2" s="2"/>
       <c r="C2" s="8"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A3" s="11"/>
       <c r="B3" s="4" t="s">
         <v>190</v>
@@ -8482,7 +8482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -8499,7 +8499,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="19.8">
+    <row r="5" spans="1:5" ht="19.8" x14ac:dyDescent="0.45">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -8516,7 +8516,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.399999999999999">
+    <row r="6" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="19.2">
+    <row r="7" spans="1:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -8551,7 +8551,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="19.2">
+    <row r="8" spans="1:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -8568,7 +8568,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17.399999999999999">
+    <row r="9" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -8577,7 +8577,7 @@
       <c r="D9" s="11"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999">
+    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -8594,7 +8594,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18.75" customHeight="1">
+    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -8611,7 +8611,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.399999999999999">
+    <row r="12" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -8628,7 +8628,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.399999999999999">
+    <row r="13" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -8637,7 +8637,7 @@
       <c r="D13" s="11"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" ht="17.399999999999999">
+    <row r="14" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="24">
         <v>11</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="19.2">
+    <row r="15" spans="1:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A15" s="24">
         <v>12</v>
       </c>
@@ -8671,7 +8671,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="17.399999999999999">
+    <row r="16" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A16" s="24">
         <v>13</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="19.2">
+    <row r="17" spans="1:6" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A17" s="24">
         <v>14</v>
       </c>
@@ -8705,12 +8705,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="17.399999999999999">
+    <row r="19" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A19" s="24">
         <v>16</v>
       </c>
@@ -8727,7 +8727,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="17.399999999999999">
+    <row r="20" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A20" s="24">
         <v>17</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="17.399999999999999">
+    <row r="21" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A21" s="24">
         <v>18</v>
       </c>
@@ -8762,7 +8762,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="19.2">
+    <row r="22" spans="1:6" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A22" s="24">
         <v>19</v>
       </c>
@@ -8780,7 +8780,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="19.2">
+    <row r="23" spans="1:6" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A23" s="24">
         <v>20</v>
       </c>
@@ -8798,14 +8798,14 @@
         <v>213</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15">
+    <row r="24" spans="1:6" ht="15" x14ac:dyDescent="0.35">
       <c r="A24" s="24">
         <v>21</v>
       </c>
       <c r="D24" s="11"/>
       <c r="F24" s="63"/>
     </row>
-    <row r="25" spans="1:6" ht="17.399999999999999">
+    <row r="25" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A25" s="24">
         <v>22</v>
       </c>
@@ -8815,7 +8815,7 @@
       <c r="C25" s="43"/>
       <c r="D25" s="11"/>
     </row>
-    <row r="26" spans="1:6" ht="19.2">
+    <row r="26" spans="1:6" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A26" s="24">
         <v>23</v>
       </c>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="D26" s="11"/>
     </row>
-    <row r="27" spans="1:6" ht="17.399999999999999">
+    <row r="27" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A27" s="24">
         <v>24</v>
       </c>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="D27" s="11"/>
     </row>
-    <row r="28" spans="1:6" ht="17.399999999999999">
+    <row r="28" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A28" s="24">
         <v>25</v>
       </c>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="D28" s="11"/>
     </row>
-    <row r="29" spans="1:6" ht="17.399999999999999">
+    <row r="29" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A29" s="24">
         <v>26</v>
       </c>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D29" s="11"/>
     </row>
-    <row r="30" spans="1:6" ht="17.399999999999999">
+    <row r="30" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A30" s="24">
         <v>27</v>
       </c>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="D30" s="11"/>
     </row>
-    <row r="31" spans="1:6" ht="17.399999999999999">
+    <row r="31" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A31" s="24">
         <v>28</v>
       </c>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="D31" s="11"/>
     </row>
-    <row r="32" spans="1:6" ht="17.399999999999999">
+    <row r="32" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A32" s="24">
         <v>29</v>
       </c>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="D32" s="11"/>
     </row>
-    <row r="33" spans="1:5" ht="17.399999999999999">
+    <row r="33" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A33" s="24">
         <v>30</v>
       </c>
@@ -8924,7 +8924,7 @@
       </c>
       <c r="D33" s="11"/>
     </row>
-    <row r="34" spans="1:5" ht="17.399999999999999">
+    <row r="34" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A34" s="24">
         <v>31</v>
       </c>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="D34" s="11"/>
     </row>
-    <row r="35" spans="1:5" ht="17.399999999999999">
+    <row r="35" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A35" s="24">
         <v>32</v>
       </c>
@@ -8952,7 +8952,7 @@
       </c>
       <c r="D35" s="11"/>
     </row>
-    <row r="36" spans="1:5" ht="17.399999999999999">
+    <row r="36" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A36" s="24">
         <v>33</v>
       </c>
@@ -8966,12 +8966,12 @@
       </c>
       <c r="D36" s="11"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="24">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="17.399999999999999">
+    <row r="38" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A38" s="24">
         <v>35</v>
       </c>
@@ -8982,12 +8982,12 @@
       <c r="D38" s="5"/>
       <c r="E38" s="4"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="24">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="19.2">
+    <row r="40" spans="1:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A40" s="24">
         <v>37</v>
       </c>
@@ -9000,7 +9000,7 @@
       <c r="D40" s="18"/>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="1:5" ht="17.399999999999999">
+    <row r="41" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A41" s="24">
         <v>38</v>
       </c>
@@ -9013,7 +9013,7 @@
       <c r="D41" s="18"/>
       <c r="E41" s="2"/>
     </row>
-    <row r="42" spans="1:5" ht="17.399999999999999">
+    <row r="42" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A42" s="24">
         <v>39</v>
       </c>
@@ -9026,7 +9026,7 @@
       <c r="D42" s="18"/>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:5" ht="17.399999999999999">
+    <row r="43" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A43" s="24">
         <v>40</v>
       </c>
@@ -9039,7 +9039,7 @@
       <c r="D43" s="18"/>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:5" ht="17.399999999999999">
+    <row r="44" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A44" s="24">
         <v>41</v>
       </c>
@@ -9052,7 +9052,7 @@
       <c r="D44" s="18"/>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="1:5" ht="17.399999999999999">
+    <row r="45" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A45" s="24">
         <v>42</v>
       </c>
@@ -9065,7 +9065,7 @@
       <c r="D45" s="18"/>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="1:5" ht="17.399999999999999">
+    <row r="46" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A46" s="24">
         <v>43</v>
       </c>
@@ -9078,7 +9078,7 @@
       <c r="D46" s="18"/>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="1:5" ht="17.399999999999999">
+    <row r="47" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A47" s="24">
         <v>44</v>
       </c>
@@ -9091,7 +9091,7 @@
       <c r="D47" s="18"/>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="1:5" ht="17.399999999999999">
+    <row r="48" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A48" s="24">
         <v>45</v>
       </c>
@@ -9100,7 +9100,7 @@
       <c r="D48" s="18"/>
       <c r="E48" s="2"/>
     </row>
-    <row r="49" spans="1:5" ht="17.399999999999999">
+    <row r="49" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A49" s="24">
         <v>46</v>
       </c>
@@ -9109,7 +9109,7 @@
       <c r="D49" s="18"/>
       <c r="E49" s="2"/>
     </row>
-    <row r="50" spans="1:5" ht="17.399999999999999">
+    <row r="50" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A50" s="24">
         <v>47</v>
       </c>
@@ -9118,7 +9118,7 @@
       <c r="D50" s="18"/>
       <c r="E50" s="2"/>
     </row>
-    <row r="51" spans="1:5" ht="17.399999999999999">
+    <row r="51" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A51" s="24">
         <v>48</v>
       </c>
@@ -9127,7 +9127,7 @@
       <c r="D51" s="18"/>
       <c r="E51" s="2"/>
     </row>
-    <row r="52" spans="1:5" ht="17.399999999999999">
+    <row r="52" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A52" s="24">
         <v>49</v>
       </c>
@@ -9138,7 +9138,7 @@
       <c r="D52" s="5"/>
       <c r="E52" s="4"/>
     </row>
-    <row r="53" spans="1:5" ht="17.399999999999999">
+    <row r="53" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A53" s="24">
         <v>50</v>
       </c>
@@ -9149,7 +9149,7 @@
       <c r="D53" s="18"/>
       <c r="E53" s="2"/>
     </row>
-    <row r="54" spans="1:5" ht="19.2">
+    <row r="54" spans="1:5" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A54" s="24">
         <v>51</v>
       </c>
@@ -9162,7 +9162,7 @@
       <c r="D54" s="18"/>
       <c r="E54" s="2"/>
     </row>
-    <row r="55" spans="1:5" ht="17.399999999999999">
+    <row r="55" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A55" s="24">
         <v>52</v>
       </c>
@@ -9175,7 +9175,7 @@
       <c r="D55" s="18"/>
       <c r="E55" s="2"/>
     </row>
-    <row r="56" spans="1:5" ht="17.399999999999999">
+    <row r="56" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A56" s="24">
         <v>53</v>
       </c>
@@ -9188,7 +9188,7 @@
       <c r="D56" s="18"/>
       <c r="E56" s="2"/>
     </row>
-    <row r="57" spans="1:5" ht="17.399999999999999">
+    <row r="57" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A57" s="24">
         <v>54</v>
       </c>
@@ -9201,7 +9201,7 @@
       <c r="D57" s="18"/>
       <c r="E57" s="2"/>
     </row>
-    <row r="58" spans="1:5" ht="17.399999999999999">
+    <row r="58" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A58" s="24">
         <v>55</v>
       </c>
@@ -9214,7 +9214,7 @@
       <c r="D58" s="18"/>
       <c r="E58" s="2"/>
     </row>
-    <row r="59" spans="1:5" ht="17.399999999999999">
+    <row r="59" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A59" s="24">
         <v>56</v>
       </c>
@@ -9227,7 +9227,7 @@
       <c r="D59" s="18"/>
       <c r="E59" s="2"/>
     </row>
-    <row r="60" spans="1:5" ht="17.399999999999999">
+    <row r="60" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A60" s="24">
         <v>57</v>
       </c>
@@ -9240,7 +9240,7 @@
       <c r="D60" s="18"/>
       <c r="E60" s="2"/>
     </row>
-    <row r="61" spans="1:5" ht="17.399999999999999">
+    <row r="61" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A61" s="24">
         <v>58</v>
       </c>
@@ -9253,7 +9253,7 @@
       <c r="D61" s="18"/>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:5" ht="17.399999999999999">
+    <row r="62" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A62" s="24">
         <v>59</v>
       </c>
@@ -9262,7 +9262,7 @@
       <c r="D62" s="18"/>
       <c r="E62" s="2"/>
     </row>
-    <row r="63" spans="1:5" ht="17.399999999999999">
+    <row r="63" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A63" s="24">
         <v>60</v>
       </c>
@@ -9271,7 +9271,7 @@
       <c r="D63" s="18"/>
       <c r="E63" s="2"/>
     </row>
-    <row r="64" spans="1:5" ht="17.399999999999999">
+    <row r="64" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A64" s="24">
         <v>61</v>
       </c>
@@ -9280,7 +9280,7 @@
       <c r="D64" s="18"/>
       <c r="E64" s="2"/>
     </row>
-    <row r="65" spans="1:6" ht="17.399999999999999">
+    <row r="65" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A65" s="24">
         <v>62</v>
       </c>
@@ -9289,7 +9289,7 @@
       <c r="D65" s="18"/>
       <c r="E65" s="2"/>
     </row>
-    <row r="66" spans="1:6" ht="17.399999999999999">
+    <row r="66" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A66" s="24">
         <v>63</v>
       </c>
@@ -9300,7 +9300,7 @@
       <c r="D66" s="18"/>
       <c r="E66" s="2"/>
     </row>
-    <row r="67" spans="1:6" ht="19.2">
+    <row r="67" spans="1:6" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A67" s="24">
         <v>64</v>
       </c>
@@ -9313,7 +9313,7 @@
       <c r="D67" s="18"/>
       <c r="E67" s="2"/>
     </row>
-    <row r="68" spans="1:6" ht="17.399999999999999">
+    <row r="68" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A68" s="24">
         <v>65</v>
       </c>
@@ -9326,7 +9326,7 @@
       <c r="D68" s="18"/>
       <c r="E68" s="2"/>
     </row>
-    <row r="69" spans="1:6" ht="17.399999999999999">
+    <row r="69" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A69" s="24">
         <v>66</v>
       </c>
@@ -9339,7 +9339,7 @@
       <c r="D69" s="18"/>
       <c r="E69" s="2"/>
     </row>
-    <row r="70" spans="1:6" ht="17.399999999999999">
+    <row r="70" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A70" s="24">
         <v>67</v>
       </c>
@@ -9352,7 +9352,7 @@
       <c r="D70" s="18"/>
       <c r="E70" s="2"/>
     </row>
-    <row r="71" spans="1:6" ht="17.399999999999999">
+    <row r="71" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A71" s="24">
         <v>68</v>
       </c>
@@ -9365,7 +9365,7 @@
       <c r="D71" s="18"/>
       <c r="E71" s="2"/>
     </row>
-    <row r="72" spans="1:6" ht="17.399999999999999">
+    <row r="72" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A72" s="24">
         <v>69</v>
       </c>
@@ -9378,7 +9378,7 @@
       <c r="D72" s="18"/>
       <c r="E72" s="2"/>
     </row>
-    <row r="73" spans="1:6" ht="17.399999999999999">
+    <row r="73" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A73" s="24">
         <v>70</v>
       </c>
@@ -9391,7 +9391,7 @@
       <c r="D73" s="18"/>
       <c r="E73" s="2"/>
     </row>
-    <row r="74" spans="1:6" ht="17.399999999999999">
+    <row r="74" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A74" s="24">
         <v>71</v>
       </c>
@@ -9404,7 +9404,7 @@
       <c r="D74" s="18"/>
       <c r="E74" s="2"/>
     </row>
-    <row r="75" spans="1:6" ht="17.399999999999999">
+    <row r="75" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A75" s="24">
         <v>72</v>
       </c>
@@ -9413,7 +9413,7 @@
       <c r="D75" s="18"/>
       <c r="E75" s="2"/>
     </row>
-    <row r="76" spans="1:6" ht="17.399999999999999">
+    <row r="76" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A76" s="24">
         <v>73</v>
       </c>
@@ -9422,7 +9422,7 @@
       <c r="D76" s="18"/>
       <c r="E76" s="2"/>
     </row>
-    <row r="77" spans="1:6" ht="17.399999999999999">
+    <row r="77" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A77" s="24">
         <v>74</v>
       </c>
@@ -9431,7 +9431,7 @@
       <c r="D77" s="18"/>
       <c r="E77" s="2"/>
     </row>
-    <row r="78" spans="1:6" ht="17.399999999999999">
+    <row r="78" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A78" s="24">
         <v>75</v>
       </c>
@@ -9440,7 +9440,7 @@
       <c r="D78" s="18"/>
       <c r="E78" s="2"/>
     </row>
-    <row r="79" spans="1:6" ht="17.399999999999999">
+    <row r="79" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A79" s="24">
         <v>76</v>
       </c>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="F79" s="25"/>
     </row>
-    <row r="80" spans="1:6" ht="17.399999999999999">
+    <row r="80" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A80" s="24">
         <v>77</v>
       </c>
@@ -9475,7 +9475,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="17.399999999999999">
+    <row r="81" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A81" s="24">
         <v>78</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="37.5" customHeight="1">
+    <row r="82" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="24">
         <v>79</v>
       </c>
@@ -9509,7 +9509,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="17.399999999999999">
+    <row r="83" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A83" s="24">
         <v>80</v>
       </c>
@@ -9526,7 +9526,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="17.399999999999999">
+    <row r="84" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A84" s="24">
         <v>81</v>
       </c>
@@ -9535,7 +9535,7 @@
       <c r="D84" s="33"/>
       <c r="E84" s="2"/>
     </row>
-    <row r="85" spans="1:5" ht="17.399999999999999">
+    <row r="85" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A85" s="24">
         <v>82</v>
       </c>
@@ -9546,7 +9546,7 @@
       <c r="D85" s="12"/>
       <c r="E85" s="25"/>
     </row>
-    <row r="86" spans="1:5" ht="17.399999999999999">
+    <row r="86" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A86" s="24">
         <v>83</v>
       </c>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="D86" s="33"/>
     </row>
-    <row r="87" spans="1:5" ht="17.399999999999999">
+    <row r="87" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A87" s="24">
         <v>84</v>
       </c>
@@ -9571,7 +9571,7 @@
       <c r="D87" s="33"/>
       <c r="E87" s="27"/>
     </row>
-    <row r="88" spans="1:5" ht="17.399999999999999">
+    <row r="88" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A88" s="24">
         <v>85</v>
       </c>
@@ -9584,7 +9584,7 @@
       <c r="D88" s="33"/>
       <c r="E88" s="2"/>
     </row>
-    <row r="89" spans="1:5" ht="17.399999999999999">
+    <row r="89" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A89" s="24">
         <v>86</v>
       </c>
@@ -9597,7 +9597,7 @@
       <c r="D89" s="9"/>
       <c r="E89" s="2"/>
     </row>
-    <row r="90" spans="1:5" ht="17.399999999999999">
+    <row r="90" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A90" s="24">
         <v>87</v>
       </c>
@@ -9610,7 +9610,7 @@
       <c r="D90" s="9"/>
       <c r="E90" s="2"/>
     </row>
-    <row r="91" spans="1:5" ht="17.399999999999999">
+    <row r="91" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A91" s="24">
         <v>88</v>
       </c>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="D91" s="9"/>
     </row>
-    <row r="92" spans="1:5" ht="17.399999999999999">
+    <row r="92" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A92" s="24">
         <v>89</v>
       </c>
@@ -9635,7 +9635,7 @@
       <c r="D92" s="9"/>
       <c r="E92" s="2"/>
     </row>
-    <row r="93" spans="1:5" ht="17.399999999999999">
+    <row r="93" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A93" s="24">
         <v>90</v>
       </c>
@@ -9648,7 +9648,7 @@
       <c r="D93" s="9"/>
       <c r="E93" s="2"/>
     </row>
-    <row r="94" spans="1:5" ht="17.399999999999999">
+    <row r="94" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A94" s="24">
         <v>91</v>
       </c>
@@ -9657,7 +9657,7 @@
       <c r="D94" s="9"/>
       <c r="E94" s="2"/>
     </row>
-    <row r="95" spans="1:5" ht="15">
+    <row r="95" spans="1:5" ht="15" x14ac:dyDescent="0.35">
       <c r="D95" s="11"/>
     </row>
   </sheetData>
@@ -9685,7 +9685,7 @@
     <tabColor rgb="FF000080"/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="37.109375" bestFit="1" customWidth="1"/>
@@ -9694,7 +9694,7 @@
     <col min="5" max="5" width="120.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>34</v>
       </c>
@@ -9702,13 +9702,13 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999">
+    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -9722,7 +9722,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -9739,7 +9739,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="20.25" customHeight="1">
+    <row r="5" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -9756,7 +9756,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.25" customHeight="1">
+    <row r="6" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -9773,7 +9773,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.399999999999999">
+    <row r="7" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17.399999999999999">
+    <row r="8" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -9807,7 +9807,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17.399999999999999">
+    <row r="9" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -9824,12 +9824,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999">
+    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.25">
       <c r="A10" s="24">
         <v>7</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C10" s="86">
         <v>25</v>
@@ -9841,12 +9841,12 @@
         <v>283</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.399999999999999">
+    <row r="11" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A11" s="24">
         <v>8</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C11" s="20">
         <v>8.0000000000000002E-3</v>
@@ -9898,7 +9898,7 @@
     <tabColor rgb="FF000080"/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.5546875" bestFit="1" customWidth="1"/>
@@ -9907,7 +9907,7 @@
     <col min="5" max="5" width="65.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>265</v>
       </c>
@@ -9915,13 +9915,13 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999">
+    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -9935,7 +9935,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -9952,7 +9952,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.399999999999999">
+    <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -9969,7 +9969,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.399999999999999">
+    <row r="6" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.399999999999999">
+    <row r="7" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -10003,7 +10003,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17.399999999999999">
+    <row r="8" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -10020,7 +10020,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="16.8" customHeight="1">
+    <row r="9" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -10037,7 +10037,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999">
+    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -10054,7 +10054,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.399999999999999">
+    <row r="11" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -10071,7 +10071,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.399999999999999">
+    <row r="12" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -10099,7 +10099,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:L20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.44140625" customWidth="1"/>
     <col min="2" max="2" width="12.88671875" customWidth="1"/>
@@ -10112,7 +10112,7 @@
     <col min="12" max="12" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="23.4">
+    <row r="1" spans="1:12" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1"/>
       <c r="B1" s="79" t="s">
         <v>17</v>
@@ -10124,14 +10124,14 @@
       <c r="G1" s="82"/>
       <c r="H1" s="82"/>
     </row>
-    <row r="2" spans="1:12" ht="17.399999999999999">
+    <row r="2" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="17.399999999999999">
+    <row r="3" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
         <v>8</v>
@@ -10153,7 +10153,7 @@
       <c r="K3" s="25"/>
       <c r="L3" s="25"/>
     </row>
-    <row r="4" spans="1:12" ht="17.399999999999999">
+    <row r="4" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -10168,7 +10168,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17.399999999999999">
+    <row r="5" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -10183,7 +10183,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="17.399999999999999">
+    <row r="6" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -10192,12 +10192,12 @@
       <c r="D6" s="9"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:12" ht="13.8">
+    <row r="7" spans="1:12" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="19.2">
+    <row r="8" spans="1:12" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -10217,7 +10217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="18">
+    <row r="9" spans="1:12" ht="18" x14ac:dyDescent="0.4">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -10240,7 +10240,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="17.399999999999999">
+    <row r="10" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>7</v>
       </c>
@@ -10263,7 +10263,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.399999999999999">
+    <row r="11" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -10286,7 +10286,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.399999999999999">
+    <row r="12" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>9</v>
       </c>
@@ -10303,7 +10303,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.399999999999999">
+    <row r="13" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="6">
         <v>10</v>
       </c>
@@ -10320,7 +10320,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.399999999999999">
+    <row r="14" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>11</v>
       </c>
@@ -10337,7 +10337,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.399999999999999">
+    <row r="15" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="6">
         <v>12</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>31.7</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.399999999999999">
+    <row r="16" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>13</v>
       </c>
@@ -10371,7 +10371,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="17.399999999999999">
+    <row r="17" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A17" s="6">
         <v>14</v>
       </c>
@@ -10388,7 +10388,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="17.399999999999999">
+    <row r="18" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>15</v>
       </c>
@@ -10405,7 +10405,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="17.399999999999999">
+    <row r="19" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A19" s="6">
         <v>16</v>
       </c>
@@ -10422,7 +10422,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="17.399999999999999">
+    <row r="20" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <v>17</v>
       </c>
@@ -10480,7 +10480,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.44140625" customWidth="1"/>
     <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
@@ -10492,7 +10492,7 @@
     <col min="15" max="15" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="23.4">
+    <row r="1" spans="1:15" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1"/>
       <c r="B1" s="79" t="s">
         <v>79</v>
@@ -10511,14 +10511,14 @@
       <c r="N1" s="82"/>
       <c r="O1" s="82"/>
     </row>
-    <row r="2" spans="1:15" ht="17.399999999999999">
+    <row r="2" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:15" ht="17.399999999999999">
+    <row r="3" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
         <v>8</v>
@@ -10543,7 +10543,7 @@
       <c r="N3" s="82"/>
       <c r="O3" s="82"/>
     </row>
-    <row r="4" spans="1:15" ht="17.399999999999999">
+    <row r="4" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -10555,10 +10555,10 @@
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="17.399999999999999">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -10574,12 +10574,12 @@
       </c>
       <c r="F5" s="2"/>
     </row>
-    <row r="6" spans="1:15" ht="17.399999999999999">
+    <row r="6" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="6">
         <v>3</v>
       </c>
       <c r="B6" s="109" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="C6" s="110">
         <v>10</v>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:15" ht="18">
+    <row r="7" spans="1:15" ht="18" x14ac:dyDescent="0.45">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:15" ht="19.2">
+    <row r="8" spans="1:15" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -10626,7 +10626,7 @@
       </c>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:15" ht="17.399999999999999">
+    <row r="9" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -10653,7 +10653,7 @@
       <c r="N9" s="82"/>
       <c r="O9" s="82"/>
     </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6">
         <v>7</v>
       </c>
@@ -10671,7 +10671,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -10682,7 +10682,7 @@
       <c r="D11" s="5"/>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:15" ht="17.399999999999999">
+    <row r="12" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="6">
         <v>9</v>
       </c>
@@ -10703,7 +10703,7 @@
       <c r="K12" s="25"/>
       <c r="L12" s="25"/>
     </row>
-    <row r="13" spans="1:15" ht="17.399999999999999">
+    <row r="13" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="6">
         <v>10</v>
       </c>
@@ -10712,7 +10712,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:15" ht="17.399999999999999">
+    <row r="14" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="6">
         <v>11</v>
       </c>
@@ -10724,7 +10724,7 @@
       <c r="E14" s="25"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:15" ht="17.399999999999999">
+    <row r="15" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="6">
         <v>12</v>
       </c>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:15" ht="18.75" customHeight="1">
+    <row r="16" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="6">
         <v>13</v>
       </c>
@@ -10766,7 +10766,7 @@
       <c r="K16" s="25"/>
       <c r="L16" s="25"/>
     </row>
-    <row r="17" spans="1:12" ht="17.399999999999999">
+    <row r="17" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A17" s="6">
         <v>14</v>
       </c>
@@ -10775,7 +10775,7 @@
       <c r="D17" s="9"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:12" ht="17.399999999999999">
+    <row r="18" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A18" s="6">
         <v>15</v>
       </c>
@@ -10786,7 +10786,7 @@
       <c r="D18" s="12"/>
       <c r="E18" s="25"/>
     </row>
-    <row r="19" spans="1:12" ht="17.399999999999999">
+    <row r="19" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A19" s="6">
         <v>16</v>
       </c>
@@ -10810,7 +10810,7 @@
       <c r="K19" s="25"/>
       <c r="L19" s="25"/>
     </row>
-    <row r="20" spans="1:12" ht="17.399999999999999">
+    <row r="20" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A20" s="6">
         <v>17</v>
       </c>
@@ -10819,7 +10819,7 @@
       <c r="D20" s="9"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:12" ht="17.399999999999999">
+    <row r="21" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A21" s="6">
         <v>18</v>
       </c>
@@ -10830,7 +10830,7 @@
       <c r="D21" s="12"/>
       <c r="E21" s="25"/>
     </row>
-    <row r="22" spans="1:12" ht="17.399999999999999">
+    <row r="22" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A22" s="6">
         <v>19</v>
       </c>
@@ -10847,7 +10847,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="17.399999999999999">
+    <row r="23" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A23" s="6">
         <v>20</v>
       </c>
@@ -10858,7 +10858,7 @@
       <c r="D23" s="5"/>
       <c r="E23" s="4"/>
     </row>
-    <row r="24" spans="1:12" ht="17.399999999999999">
+    <row r="24" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A24" s="6">
         <v>21</v>
       </c>
@@ -10917,7 +10917,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="20.5546875" customWidth="1"/>
@@ -10926,7 +10926,7 @@
     <col min="5" max="5" width="67.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>35</v>
       </c>
@@ -10934,13 +10934,13 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="18">
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B2" s="25"/>
       <c r="C2" s="12"/>
       <c r="D2" s="26"/>
       <c r="E2" s="25"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>49</v>
       </c>
@@ -10954,27 +10954,27 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
       <c r="B4" s="109" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C4" s="110">
         <v>1</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="17.399999999999999">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <v>2</v>
       </c>
       <c r="B5" s="109" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C5" s="111" t="s">
         <v>293</v>
@@ -10984,7 +10984,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.399999999999999">
+    <row r="6" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -11001,7 +11001,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18.75" customHeight="1">
+    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -11018,7 +11018,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18">
+    <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -11035,7 +11035,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18">
+    <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -11046,7 +11046,7 @@
       <c r="D9" s="23"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999">
+    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -11063,7 +11063,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18">
+    <row r="11" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -11080,7 +11080,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.25" customHeight="1">
+    <row r="12" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.25" customHeight="1">
+    <row r="13" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -11108,7 +11108,7 @@
       <c r="D13" s="19"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" ht="17.25" customHeight="1">
+    <row r="14" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="24">
         <v>11</v>
       </c>
@@ -11121,7 +11121,7 @@
       <c r="D14" s="19"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" ht="18">
+    <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" s="24">
         <v>12</v>
       </c>
@@ -11134,7 +11134,7 @@
       <c r="D15" s="19"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" ht="18">
+    <row r="16" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" s="24">
         <v>13</v>
       </c>
@@ -11147,7 +11147,7 @@
       <c r="D16" s="19"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" ht="18">
+    <row r="17" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A17" s="24">
         <v>14</v>
       </c>
@@ -11160,7 +11160,7 @@
       <c r="D17" s="19"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" ht="18">
+    <row r="18" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A18" s="24">
         <v>15</v>
       </c>
@@ -11173,7 +11173,7 @@
       <c r="D18" s="19"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5" ht="18">
+    <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A19" s="24">
         <v>16</v>
       </c>
@@ -11186,7 +11186,7 @@
       <c r="D19" s="19"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5" ht="18">
+    <row r="20" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A20" s="24">
         <v>17</v>
       </c>
@@ -11199,127 +11199,127 @@
       <c r="D20" s="19"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="41" spans="4:4" ht="15">
+    <row r="41" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D41" s="11"/>
     </row>
-    <row r="42" spans="4:4" ht="15">
+    <row r="42" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D42" s="11"/>
     </row>
-    <row r="43" spans="4:4" ht="15">
+    <row r="43" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D43" s="11"/>
     </row>
-    <row r="44" spans="4:4" ht="15">
+    <row r="44" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D44" s="11"/>
     </row>
-    <row r="45" spans="4:4" ht="15">
+    <row r="45" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D45" s="11"/>
     </row>
-    <row r="46" spans="4:4" ht="15">
+    <row r="46" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D46" s="11"/>
     </row>
-    <row r="47" spans="4:4" ht="15">
+    <row r="47" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D47" s="11"/>
     </row>
-    <row r="48" spans="4:4" ht="15">
+    <row r="48" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D48" s="11"/>
     </row>
-    <row r="49" spans="4:4" ht="15">
+    <row r="49" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D49" s="11"/>
     </row>
-    <row r="50" spans="4:4" ht="15">
+    <row r="50" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D50" s="11"/>
     </row>
-    <row r="51" spans="4:4" ht="15">
+    <row r="51" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D51" s="11"/>
     </row>
-    <row r="52" spans="4:4" ht="15">
+    <row r="52" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D52" s="11"/>
     </row>
-    <row r="53" spans="4:4" ht="15">
+    <row r="53" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D53" s="11"/>
     </row>
-    <row r="54" spans="4:4" ht="15">
+    <row r="54" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D54" s="11"/>
     </row>
-    <row r="55" spans="4:4" ht="15">
+    <row r="55" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D55" s="11"/>
     </row>
-    <row r="56" spans="4:4" ht="15">
+    <row r="56" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D56" s="11"/>
     </row>
-    <row r="57" spans="4:4" ht="15">
+    <row r="57" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D57" s="11"/>
     </row>
-    <row r="58" spans="4:4" ht="15">
+    <row r="58" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D58" s="11"/>
     </row>
-    <row r="59" spans="4:4" ht="15">
+    <row r="59" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D59" s="11"/>
     </row>
-    <row r="60" spans="4:4" ht="15">
+    <row r="60" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D60" s="11"/>
     </row>
-    <row r="61" spans="4:4" ht="15">
+    <row r="61" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D61" s="11"/>
     </row>
-    <row r="62" spans="4:4" ht="15">
+    <row r="62" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D62" s="11"/>
     </row>
-    <row r="63" spans="4:4" ht="15">
+    <row r="63" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D63" s="11"/>
     </row>
-    <row r="64" spans="4:4" ht="15">
+    <row r="64" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D64" s="11"/>
     </row>
-    <row r="65" spans="4:4" ht="15">
+    <row r="65" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D65" s="11"/>
     </row>
-    <row r="66" spans="4:4" ht="15">
+    <row r="66" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D66" s="11"/>
     </row>
-    <row r="67" spans="4:4" ht="15">
+    <row r="67" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D67" s="11"/>
     </row>
-    <row r="68" spans="4:4" ht="15">
+    <row r="68" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D68" s="11"/>
     </row>
-    <row r="69" spans="4:4" ht="15">
+    <row r="69" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D69" s="11"/>
     </row>
-    <row r="70" spans="4:4" ht="15">
+    <row r="70" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D70" s="11"/>
     </row>
-    <row r="71" spans="4:4" ht="15">
+    <row r="71" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D71" s="11"/>
     </row>
-    <row r="72" spans="4:4" ht="15">
+    <row r="72" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D72" s="11"/>
     </row>
-    <row r="73" spans="4:4" ht="15">
+    <row r="73" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D73" s="11"/>
     </row>
-    <row r="74" spans="4:4" ht="15">
+    <row r="74" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D74" s="11"/>
     </row>
-    <row r="75" spans="4:4" ht="15">
+    <row r="75" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D75" s="11"/>
     </row>
-    <row r="76" spans="4:4" ht="15">
+    <row r="76" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D76" s="11"/>
     </row>
-    <row r="77" spans="4:4" ht="15">
+    <row r="77" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D77" s="11"/>
     </row>
-    <row r="78" spans="4:4" ht="15">
+    <row r="78" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D78" s="11"/>
     </row>
-    <row r="79" spans="4:4" ht="15">
+    <row r="79" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D79" s="11"/>
     </row>
-    <row r="80" spans="4:4" ht="15">
+    <row r="80" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D80" s="11"/>
     </row>
-    <row r="81" spans="4:4" ht="15">
+    <row r="81" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D81" s="11"/>
     </row>
   </sheetData>
@@ -11352,7 +11352,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:E81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="37.88671875" bestFit="1" customWidth="1"/>
@@ -11361,7 +11361,7 @@
     <col min="5" max="5" width="67.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>35</v>
       </c>
@@ -11369,13 +11369,13 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="18">
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="B2" s="25"/>
       <c r="C2" s="12"/>
       <c r="D2" s="26"/>
       <c r="E2" s="25"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>49</v>
       </c>
@@ -11389,27 +11389,27 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
       <c r="B4" s="109" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C4" s="110">
         <v>1</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="17.399999999999999">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <v>2</v>
       </c>
       <c r="B5" s="109" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C5" s="111" t="s">
         <v>284</v>
@@ -11419,12 +11419,12 @@
         <v>258</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.399999999999999">
+    <row r="6" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A6" s="24">
         <v>3</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C6" s="20">
         <v>8</v>
@@ -11436,12 +11436,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18.75" customHeight="1">
+    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="24">
         <v>4</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C7" s="20">
         <v>8</v>
@@ -11453,12 +11453,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18">
+    <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A8" s="24">
         <v>5</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C8" s="20">
         <v>1</v>
@@ -11470,7 +11470,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18">
+    <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -11481,12 +11481,12 @@
       <c r="D9" s="23"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999">
+    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A10" s="24">
         <v>7</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C10" s="20">
         <v>0.01</v>
@@ -11498,12 +11498,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18">
+    <row r="11" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A11" s="24">
         <v>8</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C11" s="20">
         <v>0.05</v>
@@ -11515,12 +11515,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.25" customHeight="1">
+    <row r="12" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="24">
         <v>9</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C12" s="20">
         <v>0.08</v>
@@ -11532,7 +11532,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.25" customHeight="1">
+    <row r="13" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -11543,7 +11543,7 @@
       <c r="D13" s="19"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" ht="17.25" customHeight="1">
+    <row r="14" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="24">
         <v>11</v>
       </c>
@@ -11556,7 +11556,7 @@
       <c r="D14" s="19"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" ht="18">
+    <row r="15" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A15" s="24">
         <v>12</v>
       </c>
@@ -11569,7 +11569,7 @@
       <c r="D15" s="19"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" ht="18">
+    <row r="16" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A16" s="24">
         <v>13</v>
       </c>
@@ -11582,7 +11582,7 @@
       <c r="D16" s="19"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" ht="18">
+    <row r="17" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A17" s="24">
         <v>14</v>
       </c>
@@ -11595,7 +11595,7 @@
       <c r="D17" s="19"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" ht="18">
+    <row r="18" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A18" s="24">
         <v>15</v>
       </c>
@@ -11608,7 +11608,7 @@
       <c r="D18" s="19"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5" ht="18">
+    <row r="19" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A19" s="24">
         <v>16</v>
       </c>
@@ -11621,7 +11621,7 @@
       <c r="D19" s="19"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5" ht="18">
+    <row r="20" spans="1:5" ht="18" x14ac:dyDescent="0.45">
       <c r="A20" s="24">
         <v>17</v>
       </c>
@@ -11634,127 +11634,127 @@
       <c r="D20" s="19"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="41" spans="4:4" ht="15">
+    <row r="41" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D41" s="11"/>
     </row>
-    <row r="42" spans="4:4" ht="15">
+    <row r="42" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D42" s="11"/>
     </row>
-    <row r="43" spans="4:4" ht="15">
+    <row r="43" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D43" s="11"/>
     </row>
-    <row r="44" spans="4:4" ht="15">
+    <row r="44" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D44" s="11"/>
     </row>
-    <row r="45" spans="4:4" ht="15">
+    <row r="45" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D45" s="11"/>
     </row>
-    <row r="46" spans="4:4" ht="15">
+    <row r="46" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D46" s="11"/>
     </row>
-    <row r="47" spans="4:4" ht="15">
+    <row r="47" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D47" s="11"/>
     </row>
-    <row r="48" spans="4:4" ht="15">
+    <row r="48" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D48" s="11"/>
     </row>
-    <row r="49" spans="4:4" ht="15">
+    <row r="49" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D49" s="11"/>
     </row>
-    <row r="50" spans="4:4" ht="15">
+    <row r="50" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D50" s="11"/>
     </row>
-    <row r="51" spans="4:4" ht="15">
+    <row r="51" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D51" s="11"/>
     </row>
-    <row r="52" spans="4:4" ht="15">
+    <row r="52" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D52" s="11"/>
     </row>
-    <row r="53" spans="4:4" ht="15">
+    <row r="53" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D53" s="11"/>
     </row>
-    <row r="54" spans="4:4" ht="15">
+    <row r="54" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D54" s="11"/>
     </row>
-    <row r="55" spans="4:4" ht="15">
+    <row r="55" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D55" s="11"/>
     </row>
-    <row r="56" spans="4:4" ht="15">
+    <row r="56" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D56" s="11"/>
     </row>
-    <row r="57" spans="4:4" ht="15">
+    <row r="57" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D57" s="11"/>
     </row>
-    <row r="58" spans="4:4" ht="15">
+    <row r="58" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D58" s="11"/>
     </row>
-    <row r="59" spans="4:4" ht="15">
+    <row r="59" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D59" s="11"/>
     </row>
-    <row r="60" spans="4:4" ht="15">
+    <row r="60" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D60" s="11"/>
     </row>
-    <row r="61" spans="4:4" ht="15">
+    <row r="61" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D61" s="11"/>
     </row>
-    <row r="62" spans="4:4" ht="15">
+    <row r="62" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D62" s="11"/>
     </row>
-    <row r="63" spans="4:4" ht="15">
+    <row r="63" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D63" s="11"/>
     </row>
-    <row r="64" spans="4:4" ht="15">
+    <row r="64" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D64" s="11"/>
     </row>
-    <row r="65" spans="4:4" ht="15">
+    <row r="65" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D65" s="11"/>
     </row>
-    <row r="66" spans="4:4" ht="15">
+    <row r="66" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D66" s="11"/>
     </row>
-    <row r="67" spans="4:4" ht="15">
+    <row r="67" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D67" s="11"/>
     </row>
-    <row r="68" spans="4:4" ht="15">
+    <row r="68" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D68" s="11"/>
     </row>
-    <row r="69" spans="4:4" ht="15">
+    <row r="69" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D69" s="11"/>
     </row>
-    <row r="70" spans="4:4" ht="15">
+    <row r="70" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D70" s="11"/>
     </row>
-    <row r="71" spans="4:4" ht="15">
+    <row r="71" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D71" s="11"/>
     </row>
-    <row r="72" spans="4:4" ht="15">
+    <row r="72" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D72" s="11"/>
     </row>
-    <row r="73" spans="4:4" ht="15">
+    <row r="73" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D73" s="11"/>
     </row>
-    <row r="74" spans="4:4" ht="15">
+    <row r="74" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D74" s="11"/>
     </row>
-    <row r="75" spans="4:4" ht="15">
+    <row r="75" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D75" s="11"/>
     </row>
-    <row r="76" spans="4:4" ht="15">
+    <row r="76" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D76" s="11"/>
     </row>
-    <row r="77" spans="4:4" ht="15">
+    <row r="77" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D77" s="11"/>
     </row>
-    <row r="78" spans="4:4" ht="15">
+    <row r="78" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D78" s="11"/>
     </row>
-    <row r="79" spans="4:4" ht="15">
+    <row r="79" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D79" s="11"/>
     </row>
-    <row r="80" spans="4:4" ht="15">
+    <row r="80" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D80" s="11"/>
     </row>
-    <row r="81" spans="4:4" ht="15">
+    <row r="81" spans="4:4" ht="15" x14ac:dyDescent="0.35">
       <c r="D81" s="11"/>
     </row>
   </sheetData>
@@ -11787,7 +11787,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.33203125" customWidth="1"/>
     <col min="2" max="2" width="12.5546875" customWidth="1"/>
@@ -11796,7 +11796,7 @@
     <col min="5" max="5" width="50.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>33</v>
       </c>
@@ -11804,13 +11804,13 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999">
+    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -11841,7 +11841,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.399999999999999">
+    <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -11858,7 +11858,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.399999999999999">
+    <row r="6" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="B6" s="22"/>
       <c r="C6" s="20"/>
       <c r="D6" s="23"/>
@@ -11883,7 +11883,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="1"/>
     <col min="2" max="3" width="12.5546875" customWidth="1"/>
@@ -11891,7 +11891,7 @@
     <col min="5" max="5" width="108.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>89</v>
       </c>
@@ -11899,13 +11899,13 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999">
+    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -11919,7 +11919,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.25" customHeight="1">
+    <row r="4" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18" customHeight="1">
+    <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="20.25" customHeight="1">
+    <row r="6" spans="1:5" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -11981,7 +11981,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.5546875" customWidth="1"/>
@@ -11990,7 +11990,7 @@
     <col min="5" max="5" width="126.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.4">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>221</v>
       </c>
@@ -11998,13 +11998,13 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:5" ht="17.399999999999999">
+    <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="11"/>
       <c r="E2" s="2"/>
     </row>
-    <row r="3" spans="1:5" ht="17.399999999999999">
+    <row r="3" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
@@ -12018,27 +12018,27 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.399999999999999">
+    <row r="4" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
       <c r="B4" s="109" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C4" s="110">
         <v>1</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="17.399999999999999">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <v>2</v>
       </c>
       <c r="B5" s="109" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C5" s="111" t="s">
         <v>294</v>
@@ -12048,12 +12048,12 @@
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.399999999999999">
+    <row r="6" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="24">
         <v>3</v>
       </c>
       <c r="B6" s="109" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C6" s="110">
         <v>4</v>
@@ -12063,7 +12063,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.399999999999999">
+    <row r="7" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -12080,7 +12080,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17.399999999999999">
+    <row r="8" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -12097,7 +12097,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17.399999999999999">
+    <row r="9" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -12114,7 +12114,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17.399999999999999">
+    <row r="10" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -12131,7 +12131,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17.399999999999999">
+    <row r="11" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -12148,7 +12148,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17.399999999999999">
+    <row r="12" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -12165,7 +12165,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17.399999999999999">
+    <row r="13" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -12182,7 +12182,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="17.399999999999999">
+    <row r="14" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A14" s="24">
         <v>11</v>
       </c>
@@ -12199,7 +12199,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="17.399999999999999">
+    <row r="15" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A15" s="24">
         <v>12</v>
       </c>
@@ -12216,7 +12216,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="17.399999999999999">
+    <row r="16" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A16" s="24">
         <v>13</v>
       </c>
@@ -12233,7 +12233,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="17.399999999999999">
+    <row r="17" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A17" s="24">
         <v>14</v>
       </c>
@@ -12250,12 +12250,12 @@
         <v>245</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="17.399999999999999">
+    <row r="18" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A18" s="24">
         <v>15</v>
       </c>
       <c r="B18" s="105" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C18" s="108">
         <v>0</v>
@@ -12267,12 +12267,12 @@
         <v>247</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="17.399999999999999">
+    <row r="19" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A19" s="24">
         <v>16</v>
       </c>
       <c r="B19" s="105" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C19" s="108">
         <v>45</v>
@@ -12284,12 +12284,12 @@
         <v>248</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="17.399999999999999">
+    <row r="20" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A20" s="24">
         <v>17</v>
       </c>
       <c r="B20" s="105" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C20" s="108">
         <v>-20</v>
@@ -12301,12 +12301,12 @@
         <v>249</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="17.399999999999999">
+    <row r="21" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A21" s="24">
         <v>18</v>
       </c>
       <c r="B21" s="105" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C21" s="108">
         <v>60</v>
@@ -12318,7 +12318,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="17.399999999999999">
+    <row r="22" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.45">
       <c r="A22" s="24">
         <v>19</v>
       </c>
@@ -12347,7 +12347,7 @@
     <tabColor indexed="18"/>
   </sheetPr>
   <dimension ref="A1:J47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5546875" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -12360,7 +12360,7 @@
     <col min="9" max="9" width="7.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="23.4">
+    <row r="1" spans="1:10" ht="23.4" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="79" t="s">
         <v>90</v>
       </c>
@@ -12368,10 +12368,10 @@
       <c r="D1" s="81"/>
       <c r="E1" s="78"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="60"/>
     </row>
-    <row r="3" spans="1:10" ht="17.399999999999999">
+    <row r="3" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A3" s="24"/>
       <c r="B3" s="4" t="s">
         <v>101</v>
@@ -12381,7 +12381,7 @@
       <c r="E3" s="4"/>
       <c r="J3" s="25"/>
     </row>
-    <row r="4" spans="1:10" ht="17.399999999999999">
+    <row r="4" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -12394,7 +12394,7 @@
       <c r="D4" s="8"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="17.399999999999999">
+    <row r="5" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -12407,7 +12407,7 @@
       <c r="D5" s="8"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="17.399999999999999">
+    <row r="6" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -12420,7 +12420,7 @@
       <c r="D6" s="8"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="17.399999999999999">
+    <row r="7" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -12433,7 +12433,7 @@
       <c r="D7" s="8"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="17.399999999999999">
+    <row r="8" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -12446,7 +12446,7 @@
       <c r="D8" s="8"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="17.399999999999999">
+    <row r="9" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -12459,7 +12459,7 @@
       <c r="D9" s="8"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="17.399999999999999">
+    <row r="10" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -12472,7 +12472,7 @@
       <c r="D10" s="8"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="17.399999999999999">
+    <row r="11" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -12485,7 +12485,7 @@
       <c r="D11" s="8"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="17.399999999999999">
+    <row r="12" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -12498,7 +12498,7 @@
       <c r="D12" s="8"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:10" ht="17.399999999999999">
+    <row r="13" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -12511,7 +12511,7 @@
       <c r="D13" s="8"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10" ht="17.399999999999999">
+    <row r="14" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A14" s="24">
         <v>11</v>
       </c>
@@ -12524,7 +12524,7 @@
       <c r="D14" s="8"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" ht="17.399999999999999">
+    <row r="15" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A15" s="24">
         <v>12</v>
       </c>
@@ -12537,7 +12537,7 @@
       <c r="D15" s="8"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" ht="17.399999999999999">
+    <row r="16" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A16" s="24">
         <v>13</v>
       </c>
@@ -12550,7 +12550,7 @@
       <c r="D16" s="8"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:8" ht="17.399999999999999">
+    <row r="17" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A17" s="24">
         <v>14</v>
       </c>
@@ -12566,12 +12566,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="24">
         <v>16</v>
       </c>
@@ -12580,7 +12580,7 @@
       <c r="D19" s="9"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:8" ht="17.399999999999999">
+    <row r="20" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A20" s="24">
         <v>17</v>
       </c>
@@ -12591,7 +12591,7 @@
       <c r="D20" s="5"/>
       <c r="E20" s="4"/>
     </row>
-    <row r="21" spans="1:8" ht="17.399999999999999">
+    <row r="21" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A21" s="24">
         <v>18</v>
       </c>
@@ -12600,7 +12600,7 @@
       <c r="D21" s="12"/>
       <c r="E21" s="25"/>
     </row>
-    <row r="22" spans="1:8" ht="17.399999999999999">
+    <row r="22" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A22" s="24">
         <v>19</v>
       </c>
@@ -12615,7 +12615,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18">
+    <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A23" s="24">
         <v>20</v>
       </c>
@@ -12630,7 +12630,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18">
+    <row r="24" spans="1:8" ht="18" x14ac:dyDescent="0.45">
       <c r="A24" s="24">
         <v>21</v>
       </c>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="D24" s="19"/>
     </row>
-    <row r="25" spans="1:8" ht="19.8">
+    <row r="25" spans="1:8" ht="19.8" x14ac:dyDescent="0.45">
       <c r="A25" s="24">
         <v>22</v>
       </c>
@@ -12664,7 +12664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="17.399999999999999">
+    <row r="26" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A26" s="24">
         <v>23</v>
       </c>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="D26" s="11"/>
     </row>
-    <row r="27" spans="1:8" ht="17.399999999999999">
+    <row r="27" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A27" s="24">
         <v>24</v>
       </c>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="D27" s="11"/>
     </row>
-    <row r="28" spans="1:8" ht="17.399999999999999">
+    <row r="28" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A28" s="24">
         <v>25</v>
       </c>
@@ -12700,7 +12700,7 @@
       </c>
       <c r="D28" s="11"/>
     </row>
-    <row r="29" spans="1:8" ht="17.399999999999999">
+    <row r="29" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A29" s="24">
         <v>26</v>
       </c>
@@ -12712,7 +12712,7 @@
       </c>
       <c r="D29" s="11"/>
     </row>
-    <row r="30" spans="1:8" ht="17.399999999999999">
+    <row r="30" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A30" s="24">
         <v>27</v>
       </c>
@@ -12724,7 +12724,7 @@
       </c>
       <c r="D30" s="11"/>
     </row>
-    <row r="31" spans="1:8" ht="17.399999999999999">
+    <row r="31" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A31" s="24">
         <v>28</v>
       </c>
@@ -12736,7 +12736,7 @@
       </c>
       <c r="D31" s="11"/>
     </row>
-    <row r="32" spans="1:8" ht="17.399999999999999">
+    <row r="32" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A32" s="24">
         <v>29</v>
       </c>
@@ -12748,7 +12748,7 @@
       </c>
       <c r="D32" s="11"/>
     </row>
-    <row r="33" spans="1:4" ht="17.399999999999999">
+    <row r="33" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A33" s="24">
         <v>30</v>
       </c>
@@ -12760,7 +12760,7 @@
       </c>
       <c r="D33" s="11"/>
     </row>
-    <row r="34" spans="1:4" ht="17.399999999999999">
+    <row r="34" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A34" s="24">
         <v>31</v>
       </c>
@@ -12772,7 +12772,7 @@
       </c>
       <c r="D34" s="11"/>
     </row>
-    <row r="35" spans="1:4" ht="17.399999999999999">
+    <row r="35" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A35" s="24">
         <v>32</v>
       </c>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="D35" s="11"/>
     </row>
-    <row r="36" spans="1:4" ht="17.399999999999999">
+    <row r="36" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A36" s="24">
         <v>33</v>
       </c>
@@ -12796,7 +12796,7 @@
       </c>
       <c r="D36" s="11"/>
     </row>
-    <row r="37" spans="1:4" ht="17.399999999999999">
+    <row r="37" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A37" s="24">
         <v>34</v>
       </c>
@@ -12808,7 +12808,7 @@
       </c>
       <c r="D37" s="11"/>
     </row>
-    <row r="38" spans="1:4" ht="17.399999999999999">
+    <row r="38" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A38" s="24">
         <v>35</v>
       </c>
@@ -12820,7 +12820,7 @@
       </c>
       <c r="D38" s="11"/>
     </row>
-    <row r="39" spans="1:4" ht="17.399999999999999">
+    <row r="39" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A39" s="24">
         <v>36</v>
       </c>
@@ -12832,7 +12832,7 @@
       </c>
       <c r="D39" s="11"/>
     </row>
-    <row r="40" spans="1:4" ht="17.399999999999999">
+    <row r="40" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A40" s="24">
         <v>37</v>
       </c>
@@ -12844,7 +12844,7 @@
       </c>
       <c r="D40" s="11"/>
     </row>
-    <row r="41" spans="1:4" ht="17.399999999999999">
+    <row r="41" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A41" s="24">
         <v>38</v>
       </c>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="D41" s="11"/>
     </row>
-    <row r="42" spans="1:4" ht="17.399999999999999">
+    <row r="42" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A42" s="24">
         <v>39</v>
       </c>
@@ -12868,7 +12868,7 @@
       </c>
       <c r="D42" s="11"/>
     </row>
-    <row r="43" spans="1:4" ht="17.399999999999999">
+    <row r="43" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A43" s="24">
         <v>40</v>
       </c>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="D43" s="11"/>
     </row>
-    <row r="44" spans="1:4" ht="17.399999999999999">
+    <row r="44" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A44" s="24">
         <v>41</v>
       </c>
@@ -12892,7 +12892,7 @@
       </c>
       <c r="D44" s="11"/>
     </row>
-    <row r="45" spans="1:4" ht="17.399999999999999">
+    <row r="45" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A45" s="24">
         <v>42</v>
       </c>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="D45" s="11"/>
     </row>
-    <row r="46" spans="1:4" ht="17.399999999999999">
+    <row r="46" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="A46" s="24">
         <v>43</v>
       </c>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="D46" s="11"/>
     </row>
-    <row r="47" spans="1:4" ht="17.399999999999999">
+    <row r="47" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.4">
       <c r="B47" s="2" t="s">
         <v>99</v>
       </c>

--- a/inputdata/inputdata_hybridAC.xlsx
+++ b/inputdata/inputdata_hybridAC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Itahisa\Desktop\pvlite\inputdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898FF1D6-F9B6-4D93-A498-D1ABC6E8A16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E119908-0417-47F6-8BFC-7E7717C02312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site" sheetId="6" r:id="rId1"/>
@@ -9849,7 +9849,7 @@
         <v>315</v>
       </c>
       <c r="C11" s="20">
-        <v>8.0000000000000002E-3</v>
+        <v>0</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>7</v>
@@ -10866,7 +10866,7 @@
         <v>295</v>
       </c>
       <c r="C24" s="8">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="D24" s="9"/>
       <c r="E24" s="2" t="s">

--- a/inputdata/inputdata_hybridAC.xlsx
+++ b/inputdata/inputdata_hybridAC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Itahisa\Desktop\pvlite\inputdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E119908-0417-47F6-8BFC-7E7717C02312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B7CED7-E6E8-4D4D-8166-B6F91DB3D1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" firstSheet="1" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="833" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site" sheetId="6" r:id="rId1"/>
@@ -10551,7 +10551,7 @@
         <v>296</v>
       </c>
       <c r="C4" s="110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
@@ -10962,7 +10962,7 @@
         <v>297</v>
       </c>
       <c r="C4" s="110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
@@ -11397,7 +11397,7 @@
         <v>299</v>
       </c>
       <c r="C4" s="110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
@@ -12026,7 +12026,7 @@
         <v>307</v>
       </c>
       <c r="C4" s="110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="110"/>
       <c r="E4" s="109" t="s">
